--- a/docs/test-assets/product-map.xlsx
+++ b/docs/test-assets/product-map.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品模块地图" sheetId="1" r:id="R66703aa3bda54e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务对象地图" sheetId="2" r:id="R38596b907a6e4887"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务链路地图" sheetId="3" r:id="R8d9d48d25fa94bdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素地图" sheetId="4" r:id="Rebfae968ce3a48fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例资产索引" sheetId="5" r:id="R24c17676a5ee45cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块能力索引" sheetId="6" r:id="R3d1f7412ace84ebc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨模块依赖关系" sheetId="7" r:id="R6b4088cb94e44a23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可复用测试数据" sheetId="8" r:id="Rd230079a351049d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更影响分析" sheetId="9" r:id="R9d642e45606747c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更记录" sheetId="10" r:id="Re7fa39b1cce643ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品模块地图" sheetId="1" r:id="R771e75efad0e4fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务对象地图" sheetId="2" r:id="R5393def3c4524ed7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务链路地图" sheetId="3" r:id="Rd550ffe7b5a1469b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素地图" sheetId="4" r:id="Reca36880d95e4b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例资产索引" sheetId="5" r:id="R468b66d7252c48a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块能力索引" sheetId="6" r:id="Rbd2903c45f784953"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨模块依赖关系" sheetId="7" r:id="R6c3deb329cbb4bee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可复用测试数据" sheetId="8" r:id="R06901367897c416e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更影响分析" sheetId="9" r:id="Re32293d25e634551"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更记录" sheetId="10" r:id="R28172dbaf51b4cbe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -343,39 +343,17 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>示例一级模块</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>示例二级模块</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>示例三级模块</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>示例页面</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>/demo</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>说明该模块负责的业务能力</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>docs/test-assets/modules/示例模块_测试设计.xlsx</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>待确认</x:v>
-      </x:c>
-      <x:c r="J2" s="9" t="str">
-        <x:v>yyyy-mm-dd</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
-        <x:v>待补充真实模块边界</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="9"/>
+      <x:c r="K2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -428,30 +406,14 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>V1</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>yyyy-mm-dd</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>AI生成/人工修改</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>新增/修改/废弃/同步</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>示例模块</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>初始化产品测试知识图谱</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>人工评审后需更新</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
@@ -523,42 +485,18 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>内部工作流</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>工作流配置模块</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>任务执行模块</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>工作流ID/名称/状态</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>草稿/启用/停用</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>工作流配置模块</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>任务执行模块</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>TC-WF-001</x:v>
-      </x:c>
-      <x:c r="J2" s="9" t="str">
-        <x:v>TC-WF-002</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
-        <x:v>docs/test-assets/modules/内部工作流_测试设计.xlsx</x:v>
-      </x:c>
-      <x:c r="L2" s="9" t="str">
-        <x:v>状态枚举需按实际页面确认</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="9"/>
+      <x:c r="K2" s="9"/>
+      <x:c r="L2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -622,42 +560,18 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>FLOW-DEMO-001</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>内部工作流生成与消费链路</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>工作流配置模块</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>任务执行模块</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>结果展示模块</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>内部工作流</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>草稿-&gt;启用-&gt;被引用-&gt;执行完成</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>TC-WF-001</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>TC-FLOW-001</x:v>
-      </x:c>
-      <x:c r="J2" s="9" t="str">
-        <x:v>AI_TEST_WORKFLOW</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
-        <x:v>跨模块状态同步延迟</x:v>
-      </x:c>
-      <x:c r="L2" s="9" t="str">
-        <x:v>docs/test-assets/modules/跨模块链路_测试设计.xlsx</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="9"/>
+      <x:c r="K2" s="9"/>
+      <x:c r="L2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -725,45 +639,19 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>示例模块</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>示例页面</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>/demo</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>新增按钮</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>按钮</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>点击</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>有新增权限</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>TC-DEMO-001</x:v>
-      </x:c>
-      <x:c r="J2" s="9" t="str">
-        <x:v>待确认</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
-        <x:v>页面实探</x:v>
-      </x:c>
-      <x:c r="L2" s="9" t="str">
-        <x:v>yyyy-mm-dd</x:v>
-      </x:c>
-      <x:c r="M2" s="9" t="str">
-        <x:v>以最终页面文案为准</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="9"/>
+      <x:c r="K2" s="9"/>
+      <x:c r="L2" s="9"/>
+      <x:c r="M2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -836,45 +724,19 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>示例模块</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>新增管理</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>TC-DEMO-001</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>新增管理-创建AI_TEST示例数据</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>功能测试</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>手动</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="J2" s="9" t="str">
-        <x:v>示例业务对象</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
-        <x:v>FLOW-DEMO-001</x:v>
-      </x:c>
-      <x:c r="L2" s="9" t="str">
-        <x:v>docs/test-assets/modules/示例模块_测试设计.xlsx</x:v>
-      </x:c>
-      <x:c r="M2" s="9" t="str">
-        <x:v>yyyy-mm-dd</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="9"/>
+      <x:c r="K2" s="9"/>
+      <x:c r="L2" s="9"/>
+      <x:c r="M2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -939,39 +801,17 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>示例模块</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>新增管理</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>示例业务对象</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>创建带 AI_TEST 标识的示例业务对象</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>草稿/启用/禁用</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>参考 TC-DEMO-001 创建测试数据</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>TC-DEMO-001</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>docs/test-assets/modules/示例模块_测试设计.xlsx</x:v>
-      </x:c>
-      <x:c r="J2" s="9" t="str">
-        <x:v>状态流转规则待确认</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
-        <x:v>yyyy-mm-dd</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="9"/>
+      <x:c r="K2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1031,39 +871,17 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>当前模块</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>依赖模块</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>内部工作流</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>已启用工作流可被引用</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>前置数据/状态同步</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>TC-WF-001</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>TC-CURRENT-001</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>作为前置条件引用，不重复复制用例</x:v>
-      </x:c>
-      <x:c r="J2" s="9" t="str">
-        <x:v>同步时延待确认</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
-        <x:v>yyyy-mm-dd</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="9"/>
+      <x:c r="K2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1123,39 +941,17 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>示例模块</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>示例业务对象</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>AI_TEST_DEMO</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>主流程/跨模块前置数据</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>仅限本次创建且带测试标识的数据</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>通过新增用例创建</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>TC-DEMO-001</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>测试后删除或禁用</x:v>
-      </x:c>
-      <x:c r="J2" s="9" t="str">
-        <x:v>真实账号、密钥、Token 必须脱敏</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
-        <x:v>yyyy-mm-dd</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="9"/>
+      <x:c r="K2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1219,42 +1015,18 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>CHG-DEMO-001</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>示例需求</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>工作流配置模块</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>任务执行模块</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="str">
-        <x:v>内部工作流</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>FLOW-DEMO-001</x:v>
-      </x:c>
-      <x:c r="G2" s="9" t="str">
-        <x:v>TC-WF-001;TC-FLOW-001</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>新增状态同步回归用例</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>中</x:v>
-      </x:c>
-      <x:c r="J2" s="9" t="str">
-        <x:v>待确认</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
-        <x:v>yyyy-mm-dd</x:v>
-      </x:c>
-      <x:c r="L2" s="9" t="str">
-        <x:v>用户确认后更新</x:v>
-      </x:c>
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="9"/>
+      <x:c r="K2" s="9"/>
+      <x:c r="L2" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/test-assets/product-map.xlsx
+++ b/docs/test-assets/product-map.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品模块地图" sheetId="1" r:id="R771e75efad0e4fab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务对象地图" sheetId="2" r:id="R5393def3c4524ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务链路地图" sheetId="3" r:id="Rd550ffe7b5a1469b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素地图" sheetId="4" r:id="Reca36880d95e4b32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例资产索引" sheetId="5" r:id="R468b66d7252c48a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块能力索引" sheetId="6" r:id="Rbd2903c45f784953"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨模块依赖关系" sheetId="7" r:id="R6c3deb329cbb4bee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可复用测试数据" sheetId="8" r:id="R06901367897c416e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更影响分析" sheetId="9" r:id="Re32293d25e634551"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更记录" sheetId="10" r:id="R28172dbaf51b4cbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品模块地图" sheetId="1" r:id="Rf57543e24ac74e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务对象地图" sheetId="2" r:id="R7002d97780114a00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务链路地图" sheetId="3" r:id="R1dda58bf1e2a4d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素地图" sheetId="4" r:id="R493a30c4da7d45e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例资产索引" sheetId="5" r:id="R34e016e0acbd410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块能力索引" sheetId="6" r:id="Rb1b131959aae4818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨模块依赖关系" sheetId="7" r:id="R81ba0369d8244390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可复用测试数据" sheetId="8" r:id="R1f18e16045784d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更影响分析" sheetId="9" r:id="Rbaafc615dcff4226"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更记录" sheetId="10" r:id="R8ccf273e88fd4c30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -343,17 +343,39 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
-      <x:c r="I2" s="9"/>
-      <x:c r="J2" s="9"/>
-      <x:c r="K2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>示例产品</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>示例一级模块</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>示例二级模块</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>示例三级模块</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>示例页面</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>/demo</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>说明该模块负责的业务能力</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>docs/test-assets/modules/示例模块_测试设计.xlsx</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str">
+        <x:v>yyyy-mm-dd</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>待补充真实模块边界</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -406,14 +428,30 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>V1</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>yyyy-mm-dd</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>AI生成/人工修改</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>新增/修改/废弃/同步</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>示例模块</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>初始化产品测试知识图谱</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>人工评审后需更新</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
@@ -485,18 +523,42 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
-      <x:c r="I2" s="9"/>
-      <x:c r="J2" s="9"/>
-      <x:c r="K2" s="9"/>
-      <x:c r="L2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>示例产品</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>内部工作流</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>工作流配置模块</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>任务执行模块</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>工作流ID/名称/状态</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>草稿/启用/停用</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>工作流配置模块</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>任务执行模块</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>TC-WF-001</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str">
+        <x:v>TC-WF-002</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>docs/test-assets/modules/内部工作流_测试设计.xlsx</x:v>
+      </x:c>
+      <x:c r="L2" s="9" t="str">
+        <x:v>状态枚举需按实际页面确认</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -560,18 +622,42 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
-      <x:c r="I2" s="9"/>
-      <x:c r="J2" s="9"/>
-      <x:c r="K2" s="9"/>
-      <x:c r="L2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>FLOW-DEMO-001</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>内部工作流生成与消费链路</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>工作流配置模块</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>任务执行模块</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>结果展示模块</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>内部工作流</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>草稿-&gt;启用-&gt;被引用-&gt;执行完成</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>TC-WF-001</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>TC-FLOW-001</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str">
+        <x:v>AI_TEST_WORKFLOW</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>跨模块状态同步延迟</x:v>
+      </x:c>
+      <x:c r="L2" s="9" t="str">
+        <x:v>docs/test-assets/modules/跨模块链路_测试设计.xlsx</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -639,19 +725,45 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
-      <x:c r="I2" s="9"/>
-      <x:c r="J2" s="9"/>
-      <x:c r="K2" s="9"/>
-      <x:c r="L2" s="9"/>
-      <x:c r="M2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>示例产品</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>示例模块</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>示例页面</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>/demo</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>新增按钮</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>按钮</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>点击</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>有新增权限</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>TC-DEMO-001</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>页面实探</x:v>
+      </x:c>
+      <x:c r="L2" s="9" t="str">
+        <x:v>yyyy-mm-dd</x:v>
+      </x:c>
+      <x:c r="M2" s="9" t="str">
+        <x:v>以最终页面文案为准</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -724,19 +836,45 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
-      <x:c r="I2" s="9"/>
-      <x:c r="J2" s="9"/>
-      <x:c r="K2" s="9"/>
-      <x:c r="L2" s="9"/>
-      <x:c r="M2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>示例产品</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>示例模块</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>新增管理</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>TC-DEMO-001</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>新增管理-创建AI_TEST示例数据</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>功能测试</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>手动</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str">
+        <x:v>示例业务对象</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>FLOW-DEMO-001</x:v>
+      </x:c>
+      <x:c r="L2" s="9" t="str">
+        <x:v>docs/test-assets/modules/示例模块_测试设计.xlsx</x:v>
+      </x:c>
+      <x:c r="M2" s="9" t="str">
+        <x:v>yyyy-mm-dd</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -801,17 +939,39 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
-      <x:c r="I2" s="9"/>
-      <x:c r="J2" s="9"/>
-      <x:c r="K2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>示例产品</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>示例模块</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>新增管理</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>示例业务对象</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>创建带 AI_TEST 标识的示例业务对象</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>草稿/启用/禁用</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>参考 TC-DEMO-001 创建测试数据</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>TC-DEMO-001</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>docs/test-assets/modules/示例模块_测试设计.xlsx</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str">
+        <x:v>状态流转规则待确认</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>yyyy-mm-dd</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -871,17 +1031,39 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
-      <x:c r="I2" s="9"/>
-      <x:c r="J2" s="9"/>
-      <x:c r="K2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>示例产品</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>当前模块</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>依赖模块</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>内部工作流</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>已启用工作流可被引用</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>前置数据/状态同步</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>TC-WF-001</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>TC-CURRENT-001</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>作为前置条件引用，不重复复制用例</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str">
+        <x:v>同步时延待确认</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>yyyy-mm-dd</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -941,17 +1123,39 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
-      <x:c r="I2" s="9"/>
-      <x:c r="J2" s="9"/>
-      <x:c r="K2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>示例产品</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>示例模块</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>示例业务对象</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>AI_TEST_DEMO</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>主流程/跨模块前置数据</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>仅限本次创建且带测试标识的数据</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>通过新增用例创建</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>TC-DEMO-001</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>测试后删除或禁用</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str">
+        <x:v>框架不做识别、脱敏、替换或交付拦截</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>yyyy-mm-dd</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1015,18 +1219,42 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-      <x:c r="G2" s="9"/>
-      <x:c r="H2" s="9"/>
-      <x:c r="I2" s="9"/>
-      <x:c r="J2" s="9"/>
-      <x:c r="K2" s="9"/>
-      <x:c r="L2" s="9"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>CHG-DEMO-001</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>示例需求</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>工作流配置模块</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>任务执行模块</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>内部工作流</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>FLOW-DEMO-001</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="str">
+        <x:v>TC-WF-001;TC-FLOW-001</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="str">
+        <x:v>新增状态同步回归用例</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>yyyy-mm-dd</x:v>
+      </x:c>
+      <x:c r="L2" s="9" t="str">
+        <x:v>用户确认后更新</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/test-assets/product-map.xlsx
+++ b/docs/test-assets/product-map.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品模块地图" sheetId="1" r:id="Rf57543e24ac74e2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务对象地图" sheetId="2" r:id="R7002d97780114a00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务链路地图" sheetId="3" r:id="R1dda58bf1e2a4d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素地图" sheetId="4" r:id="R493a30c4da7d45e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例资产索引" sheetId="5" r:id="R34e016e0acbd410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块能力索引" sheetId="6" r:id="Rb1b131959aae4818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨模块依赖关系" sheetId="7" r:id="R81ba0369d8244390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可复用测试数据" sheetId="8" r:id="R1f18e16045784d6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更影响分析" sheetId="9" r:id="Rbaafc615dcff4226"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更记录" sheetId="10" r:id="R8ccf273e88fd4c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品模块地图" sheetId="1" r:id="R66703aa3bda54e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务对象地图" sheetId="2" r:id="R38596b907a6e4887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务链路地图" sheetId="3" r:id="R8d9d48d25fa94bdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素地图" sheetId="4" r:id="Rebfae968ce3a48fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例资产索引" sheetId="5" r:id="R24c17676a5ee45cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块能力索引" sheetId="6" r:id="R3d1f7412ace84ebc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨模块依赖关系" sheetId="7" r:id="R6b4088cb94e44a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可复用测试数据" sheetId="8" r:id="Rd230079a351049d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更影响分析" sheetId="9" r:id="R9d642e45606747c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更记录" sheetId="10" r:id="Re7fa39b1cce643ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1151,7 +1151,7 @@
         <x:v>测试后删除或禁用</x:v>
       </x:c>
       <x:c r="J2" s="9" t="str">
-        <x:v>框架不做识别、脱敏、替换或交付拦截</x:v>
+        <x:v>真实账号、密钥、Token 必须脱敏</x:v>
       </x:c>
       <x:c r="K2" s="9" t="str">
         <x:v>yyyy-mm-dd</x:v>
